--- a/artfynd/A 30320-2026 artfynd.xlsx
+++ b/artfynd/A 30320-2026 artfynd.xlsx
@@ -919,7 +919,7 @@
         <v>136104297</v>
       </c>
       <c r="B4" t="n">
-        <v>96927</v>
+        <v>96930</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>136040191</v>
       </c>
       <c r="B5" t="n">
-        <v>96645</v>
+        <v>96648</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>136040349</v>
       </c>
       <c r="B6" t="n">
-        <v>92316</v>
+        <v>92319</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         <v>136042696</v>
       </c>
       <c r="B7" t="n">
-        <v>92123</v>
+        <v>92126</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>136043472</v>
       </c>
       <c r="B8" t="n">
-        <v>92123</v>
+        <v>92126</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>136076669</v>
       </c>
       <c r="B9" t="n">
-        <v>92123</v>
+        <v>92126</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         <v>136076792</v>
       </c>
       <c r="B10" t="n">
-        <v>92123</v>
+        <v>92126</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>136040303</v>
       </c>
       <c r="B11" t="n">
-        <v>91461</v>
+        <v>91463</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>136043436</v>
       </c>
       <c r="B12" t="n">
-        <v>92780</v>
+        <v>92783</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -3763,7 +3763,7 @@
         <v>136043853</v>
       </c>
       <c r="B30" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 30320-2026 artfynd.xlsx
+++ b/artfynd/A 30320-2026 artfynd.xlsx
@@ -919,7 +919,7 @@
         <v>136104297</v>
       </c>
       <c r="B4" t="n">
-        <v>96930</v>
+        <v>96931</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>136040191</v>
       </c>
       <c r="B5" t="n">
-        <v>96648</v>
+        <v>96649</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>136040349</v>
       </c>
       <c r="B6" t="n">
-        <v>92319</v>
+        <v>92320</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         <v>136042696</v>
       </c>
       <c r="B7" t="n">
-        <v>92126</v>
+        <v>92127</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>136043472</v>
       </c>
       <c r="B8" t="n">
-        <v>92126</v>
+        <v>92127</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>136076669</v>
       </c>
       <c r="B9" t="n">
-        <v>92126</v>
+        <v>92127</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         <v>136076792</v>
       </c>
       <c r="B10" t="n">
-        <v>92126</v>
+        <v>92127</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>136043436</v>
       </c>
       <c r="B12" t="n">
-        <v>92783</v>
+        <v>92784</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -3763,7 +3763,7 @@
         <v>136043853</v>
       </c>
       <c r="B30" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 30320-2026 artfynd.xlsx
+++ b/artfynd/A 30320-2026 artfynd.xlsx
@@ -919,7 +919,7 @@
         <v>136104297</v>
       </c>
       <c r="B4" t="n">
-        <v>96931</v>
+        <v>96936</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
